--- a/Datas/CharacterGroupData.xlsx
+++ b/Datas/CharacterGroupData.xlsx
@@ -1027,10 +1027,10 @@
         <v>8</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>4100</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>9</v>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>4101</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         <v>10</v>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>4102</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1096,10 +1096,10 @@
         <v>11</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>4103</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1119,10 +1119,10 @@
         <v>12</v>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>4104</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v>13</v>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>4105</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>14</v>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>4106</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1188,10 +1188,10 @@
         <v>15</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>4107</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>16</v>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>4108</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>17</v>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>4109</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>18</v>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>4110</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1280,10 +1280,10 @@
         <v>19</v>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>4111</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>20</v>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>4112</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>21</v>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>4113</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1349,10 +1349,10 @@
         <v>22</v>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>4114</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1372,10 +1372,10 @@
         <v>23</v>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>4115</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>24</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>4116</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>25</v>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>4117</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1441,10 +1441,10 @@
         <v>26</v>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>4118</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1464,10 +1464,10 @@
         <v>27</v>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>4119</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1487,10 +1487,10 @@
         <v>28</v>
       </c>
       <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>4120</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>29</v>
       </c>
       <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>4121</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1533,10 +1533,10 @@
         <v>30</v>
       </c>
       <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>4122</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>31</v>
       </c>
       <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>4123</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>32</v>
       </c>
       <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>4124</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>33</v>
       </c>
       <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>4125</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1625,10 +1625,10 @@
         <v>34</v>
       </c>
       <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
         <v>4126</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1648,10 +1648,10 @@
         <v>35</v>
       </c>
       <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
         <v>4127</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1671,10 +1671,10 @@
         <v>36</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
         <v>4128</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>37</v>
       </c>
       <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
         <v>4129</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1717,10 +1717,10 @@
         <v>38</v>
       </c>
       <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>4130</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>39</v>
       </c>
       <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>4131</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1763,10 +1763,10 @@
         <v>40</v>
       </c>
       <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>4132</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>41</v>
       </c>
       <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
         <v>4133</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1809,10 +1809,10 @@
         <v>42</v>
       </c>
       <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>4134</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1832,10 +1832,10 @@
         <v>43</v>
       </c>
       <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
         <v>4135</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>44</v>
       </c>
       <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
         <v>4136</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1878,10 +1878,10 @@
         <v>45</v>
       </c>
       <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>4137</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>46</v>
       </c>
       <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>4138</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1924,10 +1924,10 @@
         <v>47</v>
       </c>
       <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>4139</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1947,10 +1947,10 @@
         <v>48</v>
       </c>
       <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
         <v>4140</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1970,10 +1970,10 @@
         <v>49</v>
       </c>
       <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
         <v>4141</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         <v>50</v>
       </c>
       <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
         <v>4142</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2016,10 +2016,10 @@
         <v>51</v>
       </c>
       <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
         <v>4143</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2039,10 +2039,10 @@
         <v>52</v>
       </c>
       <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
         <v>4144</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>53</v>
       </c>
       <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
         <v>4145</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2085,10 +2085,10 @@
         <v>54</v>
       </c>
       <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
         <v>4146</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2108,10 +2108,10 @@
         <v>55</v>
       </c>
       <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
         <v>4147</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2131,10 +2131,10 @@
         <v>56</v>
       </c>
       <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
         <v>4148</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2154,10 +2154,10 @@
         <v>57</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
         <v>4149</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>58</v>
       </c>
       <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
         <v>4150</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>59</v>
       </c>
       <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>4151</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2223,10 +2223,10 @@
         <v>60</v>
       </c>
       <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
         <v>4152</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2246,10 +2246,10 @@
         <v>61</v>
       </c>
       <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
         <v>4153</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2269,10 +2269,10 @@
         <v>62</v>
       </c>
       <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
         <v>4154</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>63</v>
       </c>
       <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
         <v>4155</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         <v>64</v>
       </c>
       <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
         <v>4156</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2338,10 +2338,10 @@
         <v>65</v>
       </c>
       <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
         <v>4157</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         <v>66</v>
       </c>
       <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>4158</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2384,10 +2384,10 @@
         <v>67</v>
       </c>
       <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
         <v>4159</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>68</v>
       </c>
       <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
         <v>4160</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2430,10 +2430,10 @@
         <v>69</v>
       </c>
       <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
         <v>4161</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2453,10 +2453,10 @@
         <v>70</v>
       </c>
       <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
         <v>4162</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2476,10 +2476,10 @@
         <v>71</v>
       </c>
       <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
         <v>4163</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2499,10 +2499,10 @@
         <v>72</v>
       </c>
       <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
         <v>4164</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>73</v>
       </c>
       <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
         <v>4165</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2545,10 +2545,10 @@
         <v>74</v>
       </c>
       <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
         <v>4166</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2568,10 +2568,10 @@
         <v>75</v>
       </c>
       <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
         <v>4167</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         <v>76</v>
       </c>
       <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
         <v>4168</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>77</v>
       </c>
       <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
         <v>4169</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         <v>78</v>
       </c>
       <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
         <v>4170</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2660,10 +2660,10 @@
         <v>79</v>
       </c>
       <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
         <v>4171</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>80</v>
       </c>
       <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
         <v>4172</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>81</v>
       </c>
       <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
         <v>4173</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2729,10 +2729,10 @@
         <v>82</v>
       </c>
       <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
         <v>4174</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>83</v>
       </c>
       <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
         <v>4175</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>84</v>
       </c>
       <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
         <v>4176</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2798,10 +2798,10 @@
         <v>85</v>
       </c>
       <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
         <v>4177</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>86</v>
       </c>
       <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
         <v>4178</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2844,10 +2844,10 @@
         <v>87</v>
       </c>
       <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
         <v>4179</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>

--- a/Datas/CharacterGroupData.xlsx
+++ b/Datas/CharacterGroupData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="209">
   <si>
     <t>id</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>极寒冰隙4</t>
+  </si>
+  <si>
+    <t>100100</t>
   </si>
 </sst>
 </file>
@@ -970,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G83"/>
+  <dimension ref="A2:G84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="7" width="12" customWidth="1"/>
@@ -1024,13 +1027,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>4100</v>
+        <v>4001</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1047,13 +1050,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1070,13 +1073,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1093,13 +1096,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1116,13 +1119,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1139,13 +1142,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1162,13 +1165,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1185,13 +1188,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1208,13 +1211,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1231,13 +1234,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1254,13 +1257,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1277,13 +1280,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1300,13 +1303,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1323,13 +1326,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1346,13 +1349,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1369,13 +1372,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1392,13 +1395,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1415,13 +1418,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1438,13 +1441,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1461,13 +1464,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1484,13 +1487,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1507,13 +1510,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1530,13 +1533,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1553,13 +1556,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1576,13 +1579,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1599,13 +1602,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1622,13 +1625,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1645,13 +1648,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1668,13 +1671,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1691,13 +1694,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1714,13 +1717,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1737,13 +1740,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1760,13 +1763,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1783,13 +1786,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1806,13 +1809,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1829,13 +1832,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1852,13 +1855,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>4136</v>
+        <v>4135</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1875,13 +1878,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1898,13 +1901,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1921,13 +1924,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>4139</v>
+        <v>4138</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1944,13 +1947,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1967,13 +1970,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1990,13 +1993,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2013,13 +2016,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>4143</v>
+        <v>4142</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2036,13 +2039,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>4144</v>
+        <v>4143</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2059,13 +2062,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2082,13 +2085,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2105,13 +2108,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2128,13 +2131,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2151,13 +2154,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2174,13 +2177,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2197,13 +2200,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2220,13 +2223,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2243,13 +2246,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2266,13 +2269,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>4154</v>
+        <v>4153</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2289,13 +2292,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2312,13 +2315,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2335,13 +2338,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2358,13 +2361,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2381,13 +2384,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2404,13 +2407,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2427,13 +2430,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2450,13 +2453,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>4162</v>
+        <v>4161</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2473,13 +2476,13 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2496,13 +2499,13 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2519,13 +2522,13 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>4165</v>
+        <v>4164</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2542,13 +2545,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2565,13 +2568,13 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2588,13 +2591,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2611,13 +2614,13 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>4169</v>
+        <v>4168</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2634,13 +2637,13 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2657,13 +2660,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2680,13 +2683,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>4172</v>
+        <v>4171</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2703,13 +2706,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>4173</v>
+        <v>4172</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2726,13 +2729,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>4174</v>
+        <v>4173</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2749,13 +2752,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>4175</v>
+        <v>4174</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2772,13 +2775,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>4176</v>
+        <v>4175</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2795,13 +2798,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>4177</v>
+        <v>4176</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2818,13 +2821,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>4178</v>
+        <v>4177</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2841,24 +2844,47 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>4178</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>87</v>
       </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="C83">
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
         <v>4179</v>
       </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-      <c r="G83">
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
         <v>0</v>
       </c>
     </row>

--- a/Datas/CharacterGroupData.xlsx
+++ b/Datas/CharacterGroupData.xlsx
@@ -1039,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">

--- a/Datas/CharacterGroupData.xlsx
+++ b/Datas/CharacterGroupData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="273">
   <si>
     <t>id</t>
   </si>
@@ -649,6 +649,198 @@
   </si>
   <si>
     <t>100100</t>
+  </si>
+  <si>
+    <t>100123</t>
+  </si>
+  <si>
+    <t>100124</t>
+  </si>
+  <si>
+    <t>100133</t>
+  </si>
+  <si>
+    <t>100134</t>
+  </si>
+  <si>
+    <t>100143</t>
+  </si>
+  <si>
+    <t>100144</t>
+  </si>
+  <si>
+    <t>100145</t>
+  </si>
+  <si>
+    <t>100146</t>
+  </si>
+  <si>
+    <t>100223</t>
+  </si>
+  <si>
+    <t>100224</t>
+  </si>
+  <si>
+    <t>100233</t>
+  </si>
+  <si>
+    <t>100234</t>
+  </si>
+  <si>
+    <t>100243</t>
+  </si>
+  <si>
+    <t>100244</t>
+  </si>
+  <si>
+    <t>100245</t>
+  </si>
+  <si>
+    <t>100246</t>
+  </si>
+  <si>
+    <t>100323</t>
+  </si>
+  <si>
+    <t>100324</t>
+  </si>
+  <si>
+    <t>100333</t>
+  </si>
+  <si>
+    <t>100334</t>
+  </si>
+  <si>
+    <t>100343</t>
+  </si>
+  <si>
+    <t>100344</t>
+  </si>
+  <si>
+    <t>100345</t>
+  </si>
+  <si>
+    <t>100346</t>
+  </si>
+  <si>
+    <t>100423</t>
+  </si>
+  <si>
+    <t>100424</t>
+  </si>
+  <si>
+    <t>100433</t>
+  </si>
+  <si>
+    <t>100434</t>
+  </si>
+  <si>
+    <t>100443</t>
+  </si>
+  <si>
+    <t>100444</t>
+  </si>
+  <si>
+    <t>100445</t>
+  </si>
+  <si>
+    <t>100446</t>
+  </si>
+  <si>
+    <t>100523</t>
+  </si>
+  <si>
+    <t>100524</t>
+  </si>
+  <si>
+    <t>100533</t>
+  </si>
+  <si>
+    <t>100534</t>
+  </si>
+  <si>
+    <t>100543</t>
+  </si>
+  <si>
+    <t>100544</t>
+  </si>
+  <si>
+    <t>100545</t>
+  </si>
+  <si>
+    <t>100546</t>
+  </si>
+  <si>
+    <t>100623</t>
+  </si>
+  <si>
+    <t>100624</t>
+  </si>
+  <si>
+    <t>100633</t>
+  </si>
+  <si>
+    <t>100634</t>
+  </si>
+  <si>
+    <t>100643</t>
+  </si>
+  <si>
+    <t>100644</t>
+  </si>
+  <si>
+    <t>100645</t>
+  </si>
+  <si>
+    <t>100646</t>
+  </si>
+  <si>
+    <t>100723</t>
+  </si>
+  <si>
+    <t>100724</t>
+  </si>
+  <si>
+    <t>100733</t>
+  </si>
+  <si>
+    <t>100734</t>
+  </si>
+  <si>
+    <t>100743</t>
+  </si>
+  <si>
+    <t>100744</t>
+  </si>
+  <si>
+    <t>100745</t>
+  </si>
+  <si>
+    <t>100746</t>
+  </si>
+  <si>
+    <t>100823</t>
+  </si>
+  <si>
+    <t>100824</t>
+  </si>
+  <si>
+    <t>100833</t>
+  </si>
+  <si>
+    <t>100834</t>
+  </si>
+  <si>
+    <t>100843</t>
+  </si>
+  <si>
+    <t>100844</t>
+  </si>
+  <si>
+    <t>100845</t>
+  </si>
+  <si>
+    <t>100846</t>
   </si>
 </sst>
 </file>
@@ -671,12 +863,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -691,8 +889,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -973,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G84"/>
+  <dimension ref="A2:G148"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="7" width="12" customWidth="1"/>
@@ -1036,16 +1235,16 @@
         <v>4001</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="E4">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>4001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1151,7 +1350,7 @@
         <v>4104</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1174,7 +1373,7 @@
         <v>4105</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1188,16 +1387,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1211,16 +1410,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>4107</v>
+        <v>4105</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1234,16 +1433,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>4108</v>
+        <v>4106</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>4102</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1257,16 +1456,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>4109</v>
+        <v>4107</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4103</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1280,16 +1479,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>4110</v>
+        <v>4106</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>4103</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1303,16 +1502,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>4111</v>
+        <v>4107</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>4102</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1326,137 +1525,137 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>4112</v>
+        <v>4108</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>4104</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
+    <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
-      <c r="C18">
-        <v>4113</v>
+      <c r="C18" s="1">
+        <v>4109</v>
       </c>
       <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
+        <v>4105</v>
+      </c>
+      <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4107</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>4114</v>
+        <v>4108</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>4105</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>23</v>
+    <row r="20" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
-      <c r="C20">
-        <v>4115</v>
+      <c r="C20" s="1">
+        <v>4109</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>4104</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4107</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>4116</v>
+        <v>4108</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>4104</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>4107</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>25</v>
+    <row r="22" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
-      <c r="C22">
-        <v>4117</v>
+      <c r="C22" s="1">
+        <v>4109</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>4105</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1464,13 +1663,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>4118</v>
+        <v>4110</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1487,13 +1686,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>4119</v>
+        <v>4111</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1510,13 +1709,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>4120</v>
+        <v>4112</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1533,13 +1732,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>4121</v>
+        <v>4113</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1556,16 +1755,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>4122</v>
+        <v>4114</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>4110</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1579,16 +1778,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>4123</v>
+        <v>4115</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1602,16 +1801,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>4124</v>
+        <v>4114</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1625,16 +1824,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>4125</v>
+        <v>4115</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>4110</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1648,16 +1847,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>4126</v>
+        <v>4116</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>4112</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1671,16 +1870,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>4127</v>
+        <v>4117</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>4113</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1694,16 +1893,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>219</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>4128</v>
+        <v>4116</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>4113</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1717,16 +1916,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>4129</v>
+        <v>4117</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>4112</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1740,137 +1939,137 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>4130</v>
+        <v>4118</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>4114</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>39</v>
+    <row r="36" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
-      <c r="C36">
-        <v>4131</v>
+      <c r="C36" s="1">
+        <v>4119</v>
       </c>
       <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
+        <v>4115</v>
+      </c>
+      <c r="E36" s="1">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4117</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>4132</v>
+        <v>4118</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>4115</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>41</v>
+    <row r="38" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
-      <c r="C38">
-        <v>4133</v>
+      <c r="C38" s="1">
+        <v>4119</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>4114</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>4117</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>4134</v>
+        <v>4118</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>4114</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>4117</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>43</v>
+    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
-      <c r="C40">
-        <v>4135</v>
+      <c r="C40" s="1">
+        <v>4119</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>4115</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1878,13 +2077,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>4136</v>
+        <v>4120</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1901,13 +2100,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>4137</v>
+        <v>4121</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1924,13 +2123,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>4138</v>
+        <v>4122</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1947,13 +2146,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>4139</v>
+        <v>4123</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1970,16 +2169,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>4140</v>
+        <v>4124</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4120</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1993,16 +2192,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>4141</v>
+        <v>4125</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2016,16 +2215,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>4142</v>
+        <v>4124</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2039,16 +2238,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>4143</v>
+        <v>4125</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>4120</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2062,16 +2261,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>4144</v>
+        <v>4126</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>4122</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2085,16 +2284,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>4145</v>
+        <v>4127</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>4123</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2108,16 +2307,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>4146</v>
+        <v>4126</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>4123</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2131,16 +2330,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>228</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>4147</v>
+        <v>4127</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>4122</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2154,137 +2353,137 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>4148</v>
+        <v>4128</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>4124</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>57</v>
+    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
-      <c r="C54">
-        <v>4149</v>
+      <c r="C54" s="1">
+        <v>4129</v>
       </c>
       <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
+        <v>4125</v>
+      </c>
+      <c r="E54" s="1">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4127</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>4150</v>
+        <v>4128</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>4125</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>59</v>
+    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
-      <c r="C56">
-        <v>4151</v>
+      <c r="C56" s="1">
+        <v>4129</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>4124</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>4127</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>4152</v>
+        <v>4128</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>4124</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>4127</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>61</v>
+    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
-      <c r="C58">
-        <v>4153</v>
+      <c r="C58" s="1">
+        <v>4129</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>4125</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2292,13 +2491,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>4154</v>
+        <v>4130</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2315,13 +2514,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60">
-        <v>4155</v>
+        <v>4131</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2338,13 +2537,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>4156</v>
+        <v>4132</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2361,13 +2560,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>4157</v>
+        <v>4133</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2384,16 +2583,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>4158</v>
+        <v>4134</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>4130</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2407,16 +2606,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>4159</v>
+        <v>4135</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>4131</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2430,16 +2629,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>4160</v>
+        <v>4134</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>4131</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2453,16 +2652,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>4161</v>
+        <v>4135</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>4130</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2476,16 +2675,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>4162</v>
+        <v>4136</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2499,16 +2698,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>4163</v>
+        <v>4137</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>4133</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2522,16 +2721,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>235</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>4164</v>
+        <v>4136</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>4133</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2545,16 +2744,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>4165</v>
+        <v>4137</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2568,137 +2767,137 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>4166</v>
+        <v>4138</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>4134</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>4136</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>75</v>
+    <row r="72" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
-      <c r="C72">
-        <v>4167</v>
+      <c r="C72" s="1">
+        <v>4139</v>
       </c>
       <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72">
+        <v>4135</v>
+      </c>
+      <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4137</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>4168</v>
+        <v>4138</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>4135</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>4136</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>77</v>
+    <row r="74" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
-      <c r="C74">
-        <v>4169</v>
+      <c r="C74" s="1">
+        <v>4139</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>4134</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>4170</v>
+        <v>4138</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>4134</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>79</v>
+    <row r="76" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
-      <c r="C76">
-        <v>4171</v>
+      <c r="C76" s="1">
+        <v>4139</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>4135</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>4136</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -2706,13 +2905,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>4172</v>
+        <v>4140</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2729,13 +2928,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>4173</v>
+        <v>4141</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2752,13 +2951,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>4174</v>
+        <v>4142</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2775,13 +2974,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>4175</v>
+        <v>4143</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2798,16 +2997,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>4176</v>
+        <v>4144</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>4140</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2821,16 +3020,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>4177</v>
+        <v>4145</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>4141</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2844,16 +3043,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>4178</v>
+        <v>4144</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>4141</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2867,24 +3066,1496 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>242</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>4145</v>
+      </c>
+      <c r="D84">
+        <v>4140</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>4146</v>
+      </c>
+      <c r="D85">
+        <v>4142</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>4147</v>
+      </c>
+      <c r="D86">
+        <v>4143</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>243</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>4146</v>
+      </c>
+      <c r="D87">
+        <v>4143</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>244</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>4147</v>
+      </c>
+      <c r="D88">
+        <v>4142</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>56</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>4148</v>
+      </c>
+      <c r="D89">
+        <v>4144</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>4146</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90" s="1">
+        <v>4149</v>
+      </c>
+      <c r="D90">
+        <v>4145</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>4147</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>245</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>4148</v>
+      </c>
+      <c r="D91">
+        <v>4145</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>4146</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92" s="1">
+        <v>4149</v>
+      </c>
+      <c r="D92">
+        <v>4144</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>4147</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>247</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>4148</v>
+      </c>
+      <c r="D93">
+        <v>4144</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>4147</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94" s="1">
+        <v>4149</v>
+      </c>
+      <c r="D94">
+        <v>4145</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>4146</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>58</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>4150</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>4151</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>60</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>4152</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>61</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>4153</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>62</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>4154</v>
+      </c>
+      <c r="D99">
+        <v>4150</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>4155</v>
+      </c>
+      <c r="D100">
+        <v>4151</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>249</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>4154</v>
+      </c>
+      <c r="D101">
+        <v>4151</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>250</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>4155</v>
+      </c>
+      <c r="D102">
+        <v>4150</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>4156</v>
+      </c>
+      <c r="D103">
+        <v>4152</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>4157</v>
+      </c>
+      <c r="D104">
+        <v>4153</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>251</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>4156</v>
+      </c>
+      <c r="D105">
+        <v>4153</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>4157</v>
+      </c>
+      <c r="D106">
+        <v>4152</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>66</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>4158</v>
+      </c>
+      <c r="D107">
+        <v>4154</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>4156</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>4159</v>
+      </c>
+      <c r="D108">
+        <v>4155</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>4157</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>253</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>4158</v>
+      </c>
+      <c r="D109">
+        <v>4155</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>4156</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>4159</v>
+      </c>
+      <c r="D110">
+        <v>4154</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>4157</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>255</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>4158</v>
+      </c>
+      <c r="D111">
+        <v>4154</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>4157</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>4159</v>
+      </c>
+      <c r="D112">
+        <v>4155</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>4156</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>68</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>4160</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>69</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <v>4161</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>70</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <v>4162</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>71</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <v>4163</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>72</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>4164</v>
+      </c>
+      <c r="D117">
+        <v>4160</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>73</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>4165</v>
+      </c>
+      <c r="D118">
+        <v>4161</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>4164</v>
+      </c>
+      <c r="D119">
+        <v>4161</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>258</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>4165</v>
+      </c>
+      <c r="D120">
+        <v>4160</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>74</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>4166</v>
+      </c>
+      <c r="D121">
+        <v>4162</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>75</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>4167</v>
+      </c>
+      <c r="D122">
+        <v>4163</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>259</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>4166</v>
+      </c>
+      <c r="D123">
+        <v>4163</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>260</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>4167</v>
+      </c>
+      <c r="D124">
+        <v>4162</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>4168</v>
+      </c>
+      <c r="D125">
+        <v>4164</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>4166</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>4169</v>
+      </c>
+      <c r="D126">
+        <v>4165</v>
+      </c>
+      <c r="E126" s="1">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>4167</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>261</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>4168</v>
+      </c>
+      <c r="D127">
+        <v>4165</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>4166</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>4169</v>
+      </c>
+      <c r="D128">
+        <v>4164</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>4167</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>263</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>4168</v>
+      </c>
+      <c r="D129">
+        <v>4164</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>4167</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>4169</v>
+      </c>
+      <c r="D130">
+        <v>4165</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>4166</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>78</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>4170</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>79</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>4171</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>80</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>4172</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>81</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>4173</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>82</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>4174</v>
+      </c>
+      <c r="D135">
+        <v>4170</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>83</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>4175</v>
+      </c>
+      <c r="D136">
+        <v>4171</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>265</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>4174</v>
+      </c>
+      <c r="D137">
+        <v>4171</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>266</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>4175</v>
+      </c>
+      <c r="D138">
+        <v>4170</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>84</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>4176</v>
+      </c>
+      <c r="D139">
+        <v>4172</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>85</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>4177</v>
+      </c>
+      <c r="D140">
+        <v>4173</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>267</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>4176</v>
+      </c>
+      <c r="D141">
+        <v>4173</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>268</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>4177</v>
+      </c>
+      <c r="D142">
+        <v>4172</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>86</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>4178</v>
+      </c>
+      <c r="D143">
+        <v>4174</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>4176</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144" s="1">
         <v>4179</v>
       </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
+      <c r="D144">
+        <v>4175</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>4177</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>269</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>4178</v>
+      </c>
+      <c r="D145">
+        <v>4175</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>4176</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>4179</v>
+      </c>
+      <c r="D146">
+        <v>4174</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>4177</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>271</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>4178</v>
+      </c>
+      <c r="D147">
+        <v>4174</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>4177</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>4179</v>
+      </c>
+      <c r="D148">
+        <v>4175</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>4176</v>
+      </c>
+      <c r="G148">
         <v>0</v>
       </c>
     </row>
